--- a/公司仪器测试数据.xlsx
+++ b/公司仪器测试数据.xlsx
@@ -2557,12 +2557,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>循环时间</t>
+          <t>循环</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>观测次数</t>
+          <t>观测时间</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
         <v>48.2</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="3">
@@ -2599,7 +2599,7 @@
         <v>51.7</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="4">
@@ -2617,7 +2617,7 @@
         <v>58.6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="5">
@@ -2635,7 +2635,7 @@
         <v>45.1</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="6">
@@ -2653,7 +2653,7 @@
         <v>48.8</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="7">
@@ -2671,7 +2671,7 @@
         <v>53.9</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="8">
@@ -2689,7 +2689,7 @@
         <v>52.2</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="9">
@@ -2707,7 +2707,7 @@
         <v>48.1</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="10">
@@ -2725,7 +2725,7 @@
         <v>49.3</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="11">
@@ -2743,7 +2743,7 @@
         <v>43.1</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="12">
@@ -2761,7 +2761,7 @@
         <v>48.8</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="13">
@@ -2779,7 +2779,7 @@
         <v>48.7</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="14">
@@ -2797,7 +2797,7 @@
         <v>51.2</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="15">
@@ -2815,7 +2815,7 @@
         <v>47.2</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="16">
@@ -2833,7 +2833,7 @@
         <v>52.4</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="17">
@@ -2851,7 +2851,7 @@
         <v>55.1</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="18">
@@ -2869,7 +2869,7 @@
         <v>50.8</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="19">
@@ -2887,7 +2887,7 @@
         <v>51.8</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="20">
@@ -2905,7 +2905,7 @@
         <v>50.3</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="21">
@@ -2923,7 +2923,7 @@
         <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>49.8</v>
       </c>
     </row>
   </sheetData>
@@ -2937,7 +2937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2948,15 +2948,10 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>设备名称</t>
+          <t>可用时间</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t>可用时间</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
         <is>
           <t>停机时间</t>
         </is>
@@ -2968,15 +2963,10 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>车床</t>
-        </is>
+      <c r="B2" t="n">
+        <v>480</v>
       </c>
       <c r="C2" t="n">
-        <v>480</v>
-      </c>
-      <c r="D2" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2986,15 +2976,10 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>铣床</t>
-        </is>
+      <c r="B3" t="n">
+        <v>480</v>
       </c>
       <c r="C3" t="n">
-        <v>480</v>
-      </c>
-      <c r="D3" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3004,15 +2989,10 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>钻床</t>
-        </is>
+      <c r="B4" t="n">
+        <v>480</v>
       </c>
       <c r="C4" t="n">
-        <v>480</v>
-      </c>
-      <c r="D4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3022,15 +3002,10 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>磨床</t>
-        </is>
+      <c r="B5" t="n">
+        <v>480</v>
       </c>
       <c r="C5" t="n">
-        <v>480</v>
-      </c>
-      <c r="D5" t="n">
         <v>35</v>
       </c>
     </row>
@@ -3040,15 +3015,10 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>冲床</t>
-        </is>
+      <c r="B6" t="n">
+        <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>480</v>
-      </c>
-      <c r="D6" t="n">
         <v>40</v>
       </c>
     </row>
@@ -3058,15 +3028,10 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>焊接机</t>
-        </is>
+      <c r="B7" t="n">
+        <v>480</v>
       </c>
       <c r="C7" t="n">
-        <v>480</v>
-      </c>
-      <c r="D7" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3076,15 +3041,10 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>注塑机</t>
-        </is>
+      <c r="B8" t="n">
+        <v>480</v>
       </c>
       <c r="C8" t="n">
-        <v>480</v>
-      </c>
-      <c r="D8" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3094,15 +3054,10 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>检测台</t>
-        </is>
+      <c r="B9" t="n">
+        <v>480</v>
       </c>
       <c r="C9" t="n">
-        <v>480</v>
-      </c>
-      <c r="D9" t="n">
         <v>15</v>
       </c>
     </row>
